--- a/consent_forms/043_eco_documentary_interview_consent_form--consent_forms.xlsx
+++ b/consent_forms/043_eco_documentary_interview_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1285,17 +1285,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_terms_choices</t>
+          <t>project_terms_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>model/actor_release_form</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Model/Actor Release Form</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1307,29 +1307,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>release_forms</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Release Forms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>project_terms_2_choices</t>
+          <t>model_release_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>release_forms</t>
+          <t>model/actor_release_form</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Release Forms</t>
+          <t>Model/Actor Release Form</t>
         </is>
       </c>
     </row>
@@ -1341,29 +1341,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>model/actor_release_form</t>
+          <t>location_release_form</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Model/Actor Release Form</t>
+          <t>Location Release Form</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>model_release_choices</t>
+          <t>consent_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>location_release_form</t>
+          <t>i_am_18-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Location Release Form</t>
+          <t>I am 18-24</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>i_am_18-24</t>
+          <t>i_am_25-54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>I am 18-24</t>
+          <t>I am 25-54</t>
         </is>
       </c>
     </row>
@@ -1392,29 +1392,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i_am_25-54</t>
+          <t>i_am_55+</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>I am 25-54</t>
+          <t>I am 55+</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>consent_2_choices</t>
+          <t>contact_consent_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>i_am_55+</t>
+          <t>i_am_18-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>I am 55+</t>
+          <t>I am 18-24</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>i_am_18-24</t>
+          <t>i_am_25-54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>I am 18-24</t>
+          <t>I am 25-54</t>
         </is>
       </c>
     </row>
@@ -1443,29 +1443,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i_am_25-54</t>
+          <t>i_am_55+</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>I am 25-54</t>
+          <t>I am 55+</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>contact_consent_2_choices</t>
+          <t>contact_terms_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i_am_55+</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>I am 55+</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1477,29 +1477,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>release_forms</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Release Forms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>contact_terms_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>release_forms</t>
+          <t>i_am_a_minor_(less_than_18)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Release Forms</t>
+          <t>I am a minor (less than 18)</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>i_am_a_minor_(less_than_18)</t>
+          <t>i_am_18-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>I am a minor (less than 18)</t>
+          <t>I am 18-24</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>i_am_18-24</t>
+          <t>i_am_25-54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>I am 18-24</t>
+          <t>I am 25-54</t>
         </is>
       </c>
     </row>
@@ -1545,29 +1545,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>i_am_25-54</t>
+          <t>i_am_55+</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>I am 25-54</t>
+          <t>I am 55+</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>consent_choices</t>
+          <t>contact_consent_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i_am_55+</t>
+          <t>i_am_18-24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>I am 55+</t>
+          <t>I am 18-24</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>i_am_18-24</t>
+          <t>i_am_25-54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>I am 18-24</t>
+          <t>I am 25-54</t>
         </is>
       </c>
     </row>
@@ -1596,29 +1596,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i_am_25-54</t>
+          <t>i_am_55+</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>I am 25-54</t>
+          <t>I am 55+</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>contact_consent_2_choices</t>
+          <t>contact_terms_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i_am_55+</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>I am 55+</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1630,29 +1630,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>release_forms</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Release Forms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>contact_terms_2_choices</t>
+          <t>project_terms_3_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>release_forms</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Release Forms</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1664,29 +1664,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>release_forms</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Release Forms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>project_terms_3_choices</t>
+          <t>consent_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>release_forms</t>
+          <t>i_am_18-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Release Forms</t>
+          <t>I am 18-24</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>i_am_18-24</t>
+          <t>i_am_25-54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>I am 18-24</t>
+          <t>I am 25-54</t>
         </is>
       </c>
     </row>
@@ -1715,29 +1715,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>i_am_25-54</t>
+          <t>i_am_55+</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>I am 25-54</t>
+          <t>I am 55+</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>consent_2_choices</t>
+          <t>contact_terms_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>i_am_55+</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>I am 55+</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1749,27 +1749,10 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>release_forms</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
-        <is>
-          <t>Terms and Conditions</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>contact_terms_3_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>release_forms</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
         <is>
           <t>Release Forms</t>
         </is>
